--- a/docs/tech/인사연동_뷰테이블_정의서.xlsx
+++ b/docs/tech/인사연동_뷰테이블_정의서.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610" activeTab="1"/>
+    <workbookView xWindow="390" yWindow="105" windowWidth="12555" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="부서" sheetId="1" r:id="rId1"/>
@@ -206,10 +206,6 @@
     <t>사번</t>
   </si>
   <si>
-    <t>상위부서 ID (최상위 부서의 경우 NULL)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>user_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -235,9 +231,6 @@
     <t>* 사용자 사진이 DB가 아닌 별도의 파일 시스템에 저장되어 있다면 이를 연동할 별도의 방법(HTTP 다운로드 같은)이 제공되어야 합니다.</t>
   </si>
   <si>
-    <t>* 최상위 부서를 나타내는 레코드는 parent_dept_id가 NULL 혹은 empty string입니다.</t>
-  </si>
-  <si>
     <t>* 이 테이블에서 삭제된 겸직은 그룹웨어에서도 삭제 처리됩니다.</t>
   </si>
   <si>
@@ -288,6 +281,12 @@
   </si>
   <si>
     <t>* 마지막 인사연동후 updatedt가 변경된 사용자 정보만이 반영됩니다.</t>
+  </si>
+  <si>
+    <t>* 최상위 부서(회사에 해당)를 나타내는 레코드는 parent_dept_id가 NULL 혹은 empty string입니다.</t>
+  </si>
+  <si>
+    <t>상위부서 ID (최상위 부서인 회사의 경우 NULL)</t>
   </si>
 </sst>
 </file>
@@ -871,7 +870,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="2:6">
@@ -889,28 +888,28 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C15" s="6"/>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" s="6"/>
     </row>
@@ -922,7 +921,7 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1009,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -1022,7 +1021,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1093,7 +1092,7 @@
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="2:6">
@@ -1217,7 +1216,7 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>16</v>
@@ -1225,7 +1224,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -1238,20 +1237,20 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -1264,32 +1263,32 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -1299,22 +1298,22 @@
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1402,7 +1401,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
@@ -1414,7 +1413,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1431,7 +1430,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="2:6">
@@ -1467,7 +1466,7 @@
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
